--- a/5/search/FY5_Missile1_results/solutions_direction_99.0.xlsx
+++ b/5/search/FY5_Missile1_results/solutions_direction_99.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>90</v>
       </c>
       <c r="B2" t="n">
-        <v>100.8</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
@@ -502,7 +502,7 @@
         <v>13000</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
@@ -511,7 +511,7 @@
         <v>13000</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1300</v>
@@ -522,37 +522,107 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99</v>
+        <v>94.5</v>
       </c>
       <c r="B3" t="n">
-        <v>92.40000000000001</v>
+        <v>118</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>12710.90910860565</v>
+        <v>12851.86922726583</v>
       </c>
       <c r="F3" t="n">
-        <v>-174.7519465801852</v>
+        <v>-117.8200739118545</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>12682.00001946622</v>
+        <v>12842.61105396994</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7728587617963</v>
+        <v>-0.1838285313453838</v>
       </c>
       <c r="J3" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>126</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12841.82646301267</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.785344805985915</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12841.82646301267</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.785344805985915</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B5" t="n">
+        <v>114</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12714.66353576662</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-198.4564667544687</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12678.99647773745</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26.73647490122272</v>
+      </c>
+      <c r="J5" t="n">
         <v>1280.4</v>
       </c>
-      <c r="K3" t="n">
-        <v>2</v>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
